--- a/data/nzd0087/nzd0087.xlsx
+++ b/data/nzd0087/nzd0087.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10130,6 +10130,36 @@
       <c r="H323" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>267.28</v>
+      </c>
+      <c r="C324" t="n">
+        <v>266.63</v>
+      </c>
+      <c r="D324" t="n">
+        <v>272.56</v>
+      </c>
+      <c r="E324" t="n">
+        <v>282.56</v>
+      </c>
+      <c r="F324" t="n">
+        <v>271.26</v>
+      </c>
+      <c r="G324" t="n">
+        <v>325.16</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -10144,7 +10174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B328"/>
+  <dimension ref="A1:B329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13427,6 +13457,16 @@
       </c>
       <c r="B328" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -13595,28 +13635,28 @@
         <v>0.0561</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6556688753358834</v>
+        <v>0.656781731006883</v>
       </c>
       <c r="J2" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K2" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2815369094104875</v>
+        <v>0.2837228137626149</v>
       </c>
       <c r="M2" t="n">
-        <v>6.338729389350207</v>
+        <v>6.324712194942751</v>
       </c>
       <c r="N2" t="n">
-        <v>55.54603752896033</v>
+        <v>55.38239016719412</v>
       </c>
       <c r="O2" t="n">
-        <v>7.452921409015416</v>
+        <v>7.441934571547517</v>
       </c>
       <c r="P2" t="n">
-        <v>248.085965916923</v>
+        <v>248.0736254725244</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13673,28 +13713,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5241606229494241</v>
+        <v>0.5226083665315328</v>
       </c>
       <c r="J3" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K3" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2431929575528389</v>
+        <v>0.243419994776881</v>
       </c>
       <c r="M3" t="n">
-        <v>5.255160929131057</v>
+        <v>5.245945997651781</v>
       </c>
       <c r="N3" t="n">
-        <v>43.28902235248075</v>
+        <v>43.17119133426398</v>
       </c>
       <c r="O3" t="n">
-        <v>6.579439364602485</v>
+        <v>6.570478775117075</v>
       </c>
       <c r="P3" t="n">
-        <v>254.9014191718117</v>
+        <v>254.9186321263002</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13751,28 +13791,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5159014361385216</v>
+        <v>0.5119192553722586</v>
       </c>
       <c r="J4" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K4" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2328650264081471</v>
+        <v>0.2310189868215043</v>
       </c>
       <c r="M4" t="n">
-        <v>5.356245665099214</v>
+        <v>5.358260024806734</v>
       </c>
       <c r="N4" t="n">
-        <v>44.3931346768977</v>
+        <v>44.36225145119941</v>
       </c>
       <c r="O4" t="n">
-        <v>6.662817322792042</v>
+        <v>6.660499339478942</v>
       </c>
       <c r="P4" t="n">
-        <v>264.6497486689304</v>
+        <v>264.6939070280166</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13829,28 +13869,28 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.479184678055027</v>
+        <v>0.475268313710872</v>
       </c>
       <c r="J5" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K5" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2252152672512218</v>
+        <v>0.2232227718451729</v>
       </c>
       <c r="M5" t="n">
-        <v>5.113468275695253</v>
+        <v>5.115677241516692</v>
       </c>
       <c r="N5" t="n">
-        <v>39.99483377296361</v>
+        <v>39.97407440020478</v>
       </c>
       <c r="O5" t="n">
-        <v>6.324146881039656</v>
+        <v>6.322505389495906</v>
       </c>
       <c r="P5" t="n">
-        <v>275.5310010603326</v>
+        <v>275.5744295818319</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13907,28 +13947,28 @@
         <v>0.041</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4377961956483075</v>
+        <v>0.4322926886604543</v>
       </c>
       <c r="J6" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K6" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1441643180768599</v>
+        <v>0.1415563021409889</v>
       </c>
       <c r="M6" t="n">
-        <v>6.083047484146149</v>
+        <v>6.089110070236445</v>
       </c>
       <c r="N6" t="n">
-        <v>57.6091407324292</v>
+        <v>57.63430953628192</v>
       </c>
       <c r="O6" t="n">
-        <v>7.590068559138922</v>
+        <v>7.591726387079682</v>
       </c>
       <c r="P6" t="n">
-        <v>267.6914746950174</v>
+        <v>267.7525030239827</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -13985,28 +14025,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05839574373611276</v>
+        <v>0.05457035799560692</v>
       </c>
       <c r="J7" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K7" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005767686088500312</v>
+        <v>0.005061726672196287</v>
       </c>
       <c r="M7" t="n">
-        <v>4.393076489951101</v>
+        <v>4.396880445494712</v>
       </c>
       <c r="N7" t="n">
-        <v>29.76209306578205</v>
+        <v>29.76828120947935</v>
       </c>
       <c r="O7" t="n">
-        <v>5.455464514207938</v>
+        <v>5.456031635674353</v>
       </c>
       <c r="P7" t="n">
-        <v>329.265265854058</v>
+        <v>329.3076855148136</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14044,7 +14084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H323"/>
+  <dimension ref="A1:H324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27613,6 +27653,48 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>-35.529618424728035,174.46024555210752</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>-35.530383392753315,174.4602164709658</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>-35.531226698352484,174.4603449942658</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>-35.532137755917766,174.4607924284678</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-35.53290172458486,174.4614199694053</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-35.53308710755836,174.46249808571125</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0087/nzd0087.xlsx
+++ b/data/nzd0087/nzd0087.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10158,6 +10158,66 @@
         <v>325.16</v>
       </c>
       <c r="H324" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>262.09</v>
+      </c>
+      <c r="C325" t="n">
+        <v>260.9</v>
+      </c>
+      <c r="D325" t="n">
+        <v>267.75</v>
+      </c>
+      <c r="E325" t="n">
+        <v>278.42</v>
+      </c>
+      <c r="F325" t="n">
+        <v>264.93</v>
+      </c>
+      <c r="G325" t="n">
+        <v>322.56</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>262.49</v>
+      </c>
+      <c r="C326" t="n">
+        <v>261.79</v>
+      </c>
+      <c r="D326" t="n">
+        <v>270.52</v>
+      </c>
+      <c r="E326" t="n">
+        <v>279.92</v>
+      </c>
+      <c r="F326" t="n">
+        <v>266.53</v>
+      </c>
+      <c r="G326" t="n">
+        <v>321.65</v>
+      </c>
+      <c r="H326" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -10174,7 +10234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B329"/>
+  <dimension ref="A1:B331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13467,6 +13527,26 @@
       </c>
       <c r="B329" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -13635,28 +13715,28 @@
         <v>0.0561</v>
       </c>
       <c r="I2" t="n">
-        <v>0.656781731006883</v>
+        <v>0.652239741867214</v>
       </c>
       <c r="J2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K2" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2837228137626149</v>
+        <v>0.2836865127562263</v>
       </c>
       <c r="M2" t="n">
-        <v>6.324712194942751</v>
+        <v>6.304360511208201</v>
       </c>
       <c r="N2" t="n">
-        <v>55.38239016719412</v>
+        <v>55.11194673699114</v>
       </c>
       <c r="O2" t="n">
-        <v>7.441934571547517</v>
+        <v>7.423742097957818</v>
       </c>
       <c r="P2" t="n">
-        <v>248.0736254725244</v>
+        <v>248.1241333421679</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -13713,28 +13793,28 @@
         <v>0.0407</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5226083665315328</v>
+        <v>0.5124906198167175</v>
       </c>
       <c r="J3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K3" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L3" t="n">
-        <v>0.243419994776881</v>
+        <v>0.2375336510671749</v>
       </c>
       <c r="M3" t="n">
-        <v>5.245945997651781</v>
+        <v>5.259645329823505</v>
       </c>
       <c r="N3" t="n">
-        <v>43.17119133426398</v>
+        <v>43.25478682369621</v>
       </c>
       <c r="O3" t="n">
-        <v>6.570478775117075</v>
+        <v>6.57683714437998</v>
       </c>
       <c r="P3" t="n">
-        <v>254.9186321263002</v>
+        <v>255.0311435119191</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -13791,28 +13871,28 @@
         <v>0.0495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5119192553722586</v>
+        <v>0.4995435392250754</v>
       </c>
       <c r="J4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K4" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2310189868215043</v>
+        <v>0.2229531902152821</v>
       </c>
       <c r="M4" t="n">
-        <v>5.358260024806734</v>
+        <v>5.382945145691482</v>
       </c>
       <c r="N4" t="n">
-        <v>44.36225145119941</v>
+        <v>44.62178929242948</v>
       </c>
       <c r="O4" t="n">
-        <v>6.660499339478942</v>
+        <v>6.679954288199095</v>
       </c>
       <c r="P4" t="n">
-        <v>264.6939070280166</v>
+        <v>264.8315223936631</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -13869,28 +13949,28 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.475268313710872</v>
+        <v>0.4630709368552108</v>
       </c>
       <c r="J5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K5" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2232227718451729</v>
+        <v>0.2147139115397653</v>
       </c>
       <c r="M5" t="n">
-        <v>5.115677241516692</v>
+        <v>5.139627148490515</v>
       </c>
       <c r="N5" t="n">
-        <v>39.97407440020478</v>
+        <v>40.23736819716657</v>
       </c>
       <c r="O5" t="n">
-        <v>6.322505389495906</v>
+        <v>6.3432931665789</v>
       </c>
       <c r="P5" t="n">
-        <v>275.5744295818319</v>
+        <v>275.7100655828183</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -13947,28 +14027,28 @@
         <v>0.041</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4322926886604543</v>
+        <v>0.4141578226258332</v>
       </c>
       <c r="J6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K6" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1415563021409889</v>
+        <v>0.1309530935913351</v>
       </c>
       <c r="M6" t="n">
-        <v>6.089110070236445</v>
+        <v>6.135204103885981</v>
       </c>
       <c r="N6" t="n">
-        <v>57.63430953628192</v>
+        <v>58.40176740854795</v>
       </c>
       <c r="O6" t="n">
-        <v>7.591726387079682</v>
+        <v>7.642104906931594</v>
       </c>
       <c r="P6" t="n">
-        <v>267.7525030239827</v>
+        <v>267.9541663502705</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -14025,28 +14105,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05457035799560692</v>
+        <v>0.04303045939992491</v>
       </c>
       <c r="J7" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="K7" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005061726672196287</v>
+        <v>0.003152541288992228</v>
       </c>
       <c r="M7" t="n">
-        <v>4.396880445494712</v>
+        <v>4.422105834264402</v>
       </c>
       <c r="N7" t="n">
-        <v>29.76828120947935</v>
+        <v>30.03908402069926</v>
       </c>
       <c r="O7" t="n">
-        <v>5.456031635674353</v>
+        <v>5.480792280382396</v>
       </c>
       <c r="P7" t="n">
-        <v>329.3076855148136</v>
+        <v>329.4360173462601</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -14084,7 +14164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27695,6 +27775,90 @@
         </is>
       </c>
     </row>
+    <row r="325">
+      <c r="A325" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>-35.52961773457505,174.46018832371593</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>-35.53038467026444,174.46015330002712</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>-35.531234223786626,174.46029275417098</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>-35.53215574648487,174.46075242659643</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>-35.53294118710604,174.4613695448979</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-35.533103930879555,174.4624781209095</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>-35.52961778776699,174.46019273438196</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>-35.530384471839916,174.46016311191832</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>-35.53122989001543,174.46032283838488</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>-35.53214922816494,174.46076692003018</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>-35.53293121237903,174.46138229043368</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>-35.533109819041236,174.46247113322693</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
